--- a/data/attendance.xlsx
+++ b/data/attendance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,7 +700,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -931,11 +931,798 @@
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="n">
-        <v>20</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4188606463</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ibrahim el hicho</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>16:54:52</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>18:05:14</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4188540927</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>imran begdouri</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>16:55:11</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>18:05:28</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1452822175</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>souhaib el mizzari</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>16:55:42</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>18:05:21</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1801818826</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>omar ellon</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>16:58:38</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4188540927</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>imran begdouri</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>21:13:26</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>22:26:15</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4188606463</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ibrahim el hicho</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>21:13:36</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>22:01:42</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1801818826</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>omar ellon</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>21:21:57</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>22:30:06</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1802112026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>hicham jaidi</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>22:25:59</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1452822175</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>souhaib el mizzari</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>22:26:05</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4188606463</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ibrahim el hicho</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>19:26:32</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4188606463</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ibrahim el hicho</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>16:05:43</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>19:32:06</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1452822175</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>souhaib el mizzari</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>16:06:04</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>19:32:46</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4188540927</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>imran begdouri</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>16:06:08</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>19:32:15</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1452822175</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>souhaib el mizzari</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>14:43:06</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4188540927</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>imran begdouri</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>14:43:15</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4188606463</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ibrahim el hicho</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>14:43:18</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3076125203</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>mouad classe</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>14:25:37</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>14:43:08</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3076075299</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>adil maimouni</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>14:32:20</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3077813539</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>mohamed affelad</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>14:42:14</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>27.75</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
         <is>
           <t>YES</t>
         </is>

--- a/data/attendance.xlsx
+++ b/data/attendance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1679,14 +1679,26 @@
           <t>14:32:20</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>19:42:14</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>15.5</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>YES</t>
@@ -1714,15 +1726,367 @@
           <t>14:42:14</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>19:42:09</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>27.75</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>4188606463</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ibrahim el hicho</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2893913171</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>reda affelad</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1452822175</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>souhaib el mizzari</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>19:41:34</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>20:32:48</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>4188540927</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>imran begdouri</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>19:41:44</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>20:32:43</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1802112026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>hicham jaidi</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2027-05-18</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1802112026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>hicham jaidi</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1801818826</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>omar ellon</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1802112026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>hicham jaidi</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
